--- a/reagent_msds_index.xlsx
+++ b/reagent_msds_index.xlsx
@@ -496,7 +496,7 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -785,7 +785,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>COVID-19 Rapid Test</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>📄 MSDS  2019-nCoV.pdf</t>
+          <t>📄 MSDS 2019-nCoV.pdf</t>
         </is>
       </c>
     </row>
@@ -829,11 +829,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -908,7 +908,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>📄 BD Calibrite™ 3-color kit-ec9d4b75.pdf</t>
+          <t>📄 BD Calibrite™ 3-color kit.pdf</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>📄 BD FACSClean™-6b97fea7.pdf</t>
+          <t>📄 BD FACSClean™.pdf</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>📄 BD FACS™ Lysing-9be88d68.pdf</t>
+          <t>📄 BD FACS™ Lysing.pdf</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>📄 BD Tritest™ CD3CD4CD45-d874fbc6.pdf</t>
+          <t>📄 BD Tritest™ CD3CD4CD45.pdf</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>📄 BD Trucount™ Tubes-c639f26c.pdf</t>
+          <t>📄 BD Trucount™ Tubes.pdf</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>📄 HIV-1 Quantitative nucleic acid test for use on the cobas® 580068008800 Systems Rev 4.1.pdf</t>
+          <t>📄 HIV-1 cobas NAT Rev 4.1.pdf</t>
         </is>
       </c>
     </row>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Novel Coronavirus Ag Test Kit — S3102E</t>
+          <t>Novel Coronavirus (2019-nCoV) Nucleic Acid Diagnostic Kit</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ตรวจหาแอนติเจน SARS-CoV-2 (Rapid Test)</t>
+          <t>ตรวจ SARS-CoV-2 Nucleic Acid</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Rapid / Lateral Flow</t>
+          <t>Nucleic Acid Diagnostic</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>📄 [PI] S3102E Noval Coronavirus V08-20220718-28c7af73.pdf</t>
+          <t>📄 [PI] S3102E Noval Coronavirus.pdf</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>น้ำยา Release ตัวอย่างสำหรับ COVID-19 Ag Test (RUO)</t>
+          <t>น้ำยา Release ตัวอย่างสำหรับ COVID-19 (RUO)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>📄 Manual-Sample-Release-Reagent-S1014E-RUO-20200623.pdf</t>
+          <t>📄 Manual-Sample-Release-Reagent-S1014E.pdf</t>
         </is>
       </c>
     </row>
